--- a/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
+++ b/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D61742EB-5CFC-4CA4-B516-3F1DD5833500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8ED756B6-D070-4DA2-BA33-E05D2F1B5233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" xr2:uid="{A601157B-3585-48CF-B7D1-6279C1EF8696}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E367BCF0-76BB-4DF1-BDDD-518273EE3548}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3019,7 +3019,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9321D03-2CC3-4DF3-BBF6-6E813A23DC9B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{328F91AF-0B8D-432A-A1F5-DAF2718C9138}">
   <dimension ref="B9:T162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11605,7 +11605,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E850513-C7EC-4D0C-B0FB-D6FF2D9182F3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{637C4294-6219-47B6-875D-9B6C703ACB2D}">
   <dimension ref="B9:T57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14245,7 +14245,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90A9B5C3-4083-487C-B393-741D87C07AFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC2BE351-2F20-4594-B8B9-F0ACF530363A}">
   <dimension ref="B9:T313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23676,7 +23676,7 @@
         <v>232</v>
       </c>
       <c r="P187" t="s">
-        <v>482</v>
+        <v>422</v>
       </c>
       <c r="Q187" t="s">
         <v>311</v>
@@ -23732,7 +23732,7 @@
         <v>232</v>
       </c>
       <c r="P188" t="s">
-        <v>422</v>
+        <v>482</v>
       </c>
       <c r="Q188" t="s">
         <v>311</v>
@@ -25916,7 +25916,7 @@
         <v>296</v>
       </c>
       <c r="P227" t="s">
-        <v>482</v>
+        <v>422</v>
       </c>
       <c r="Q227" t="s">
         <v>311</v>
@@ -25972,7 +25972,7 @@
         <v>296</v>
       </c>
       <c r="P228" t="s">
-        <v>422</v>
+        <v>482</v>
       </c>
       <c r="Q228" t="s">
         <v>311</v>
@@ -29031,7 +29031,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6669C07-BDEA-4A51-8A18-8EB465C71483}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C49352-9198-4229-9227-513B0F34409C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
+++ b/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8ED756B6-D070-4DA2-BA33-E05D2F1B5233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1435708-DD85-44BE-869E-E0D29E2B632F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E367BCF0-76BB-4DF1-BDDD-518273EE3548}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EE5EA15E-C6B9-494F-8899-E53BDADD03F7}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3019,7 +3019,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{328F91AF-0B8D-432A-A1F5-DAF2718C9138}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40F67264-4228-432E-9A8F-272BC368444F}">
   <dimension ref="B9:T162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3098,19 +3098,19 @@
         <v>17</v>
       </c>
       <c r="E11">
-        <v>9.3024000000000037E-2</v>
+        <v>0.18139680000000002</v>
       </c>
       <c r="F11">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G11">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H11">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I11">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J11" t="s">
         <v>15</v>
@@ -3154,19 +3154,19 @@
         <v>17</v>
       </c>
       <c r="E12">
-        <v>9.3024000000000037E-2</v>
+        <v>0.1813968</v>
       </c>
       <c r="F12">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G12">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H12">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I12">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J12" t="s">
         <v>18</v>
@@ -3210,19 +3210,19 @@
         <v>17</v>
       </c>
       <c r="E13">
-        <v>9.3024000000000037E-2</v>
+        <v>0.18139680000000002</v>
       </c>
       <c r="F13">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G13">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H13">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I13">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J13" t="s">
         <v>19</v>
@@ -3266,19 +3266,19 @@
         <v>17</v>
       </c>
       <c r="E14">
-        <v>9.3024000000000037E-2</v>
+        <v>0.18139680000000002</v>
       </c>
       <c r="F14">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G14">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H14">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I14">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J14" t="s">
         <v>20</v>
@@ -3322,19 +3322,19 @@
         <v>17</v>
       </c>
       <c r="E15">
-        <v>0.21236400000000008</v>
+        <v>0.28017360000000002</v>
       </c>
       <c r="F15">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G15">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H15">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I15">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J15" t="s">
         <v>21</v>
@@ -3378,19 +3378,19 @@
         <v>17</v>
       </c>
       <c r="E16">
-        <v>0.21236400000000008</v>
+        <v>0.28017360000000002</v>
       </c>
       <c r="F16">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G16">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H16">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I16">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J16" t="s">
         <v>22</v>
@@ -3434,19 +3434,19 @@
         <v>24</v>
       </c>
       <c r="E17">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F17">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G17">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H17">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I17">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J17" t="s">
         <v>23</v>
@@ -3490,19 +3490,19 @@
         <v>24</v>
       </c>
       <c r="E18">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F18">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G18">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H18">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I18">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J18" t="s">
         <v>25</v>
@@ -3546,19 +3546,19 @@
         <v>24</v>
       </c>
       <c r="E19">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F19">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G19">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H19">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I19">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J19" t="s">
         <v>26</v>
@@ -3602,19 +3602,19 @@
         <v>24</v>
       </c>
       <c r="E20">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F20">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G20">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H20">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I20">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J20" t="s">
         <v>27</v>
@@ -3658,19 +3658,19 @@
         <v>24</v>
       </c>
       <c r="E21">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F21">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G21">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H21">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I21">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J21" t="s">
         <v>28</v>
@@ -3714,19 +3714,19 @@
         <v>24</v>
       </c>
       <c r="E22">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F22">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G22">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H22">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I22">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J22" t="s">
         <v>29</v>
@@ -3770,19 +3770,19 @@
         <v>24</v>
       </c>
       <c r="E23">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F23">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G23">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H23">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I23">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J23" t="s">
         <v>30</v>
@@ -3826,19 +3826,19 @@
         <v>24</v>
       </c>
       <c r="E24">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F24">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G24">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H24">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I24">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J24" t="s">
         <v>31</v>
@@ -3882,19 +3882,19 @@
         <v>33</v>
       </c>
       <c r="E25">
-        <v>0.21236400000000008</v>
+        <v>0.28017360000000002</v>
       </c>
       <c r="F25">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G25">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H25">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I25">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J25" t="s">
         <v>32</v>
@@ -3938,19 +3938,19 @@
         <v>33</v>
       </c>
       <c r="E26">
-        <v>0.21236400000000008</v>
+        <v>0.28017360000000002</v>
       </c>
       <c r="F26">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G26">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H26">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I26">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J26" t="s">
         <v>34</v>
@@ -3994,19 +3994,19 @@
         <v>33</v>
       </c>
       <c r="E27">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F27">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G27">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H27">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I27">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J27" t="s">
         <v>35</v>
@@ -4050,19 +4050,19 @@
         <v>33</v>
       </c>
       <c r="E28">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F28">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G28">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H28">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I28">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J28" t="s">
         <v>36</v>
@@ -4106,19 +4106,19 @@
         <v>33</v>
       </c>
       <c r="E29">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F29">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G29">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H29">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I29">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J29" t="s">
         <v>37</v>
@@ -4162,19 +4162,19 @@
         <v>39</v>
       </c>
       <c r="E30">
-        <v>8.7552000000000019E-2</v>
+        <v>0.1707264</v>
       </c>
       <c r="F30">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G30">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H30">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I30">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J30" t="s">
         <v>38</v>
@@ -4218,19 +4218,19 @@
         <v>39</v>
       </c>
       <c r="E31">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F31">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G31">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H31">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I31">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J31" t="s">
         <v>40</v>
@@ -4274,19 +4274,19 @@
         <v>39</v>
       </c>
       <c r="E32">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F32">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G32">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H32">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I32">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J32" t="s">
         <v>41</v>
@@ -4330,19 +4330,19 @@
         <v>43</v>
       </c>
       <c r="E33">
-        <v>8.7552000000000019E-2</v>
+        <v>0.1707264</v>
       </c>
       <c r="F33">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G33">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H33">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I33">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J33" t="s">
         <v>42</v>
@@ -4386,19 +4386,19 @@
         <v>43</v>
       </c>
       <c r="E34">
-        <v>8.7552000000000019E-2</v>
+        <v>0.1707264</v>
       </c>
       <c r="F34">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G34">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H34">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I34">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J34" t="s">
         <v>44</v>
@@ -4442,19 +4442,19 @@
         <v>43</v>
       </c>
       <c r="E35">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F35">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G35">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H35">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I35">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J35" t="s">
         <v>45</v>
@@ -4498,19 +4498,19 @@
         <v>43</v>
       </c>
       <c r="E36">
-        <v>8.7552000000000019E-2</v>
+        <v>0.1707264</v>
       </c>
       <c r="F36">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G36">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H36">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I36">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J36" t="s">
         <v>46</v>
@@ -4554,19 +4554,19 @@
         <v>43</v>
       </c>
       <c r="E37">
-        <v>8.7552000000000019E-2</v>
+        <v>0.1707264</v>
       </c>
       <c r="F37">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G37">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H37">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I37">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J37" t="s">
         <v>47</v>
@@ -4610,19 +4610,19 @@
         <v>43</v>
       </c>
       <c r="E38">
-        <v>8.7552000000000019E-2</v>
+        <v>0.1707264</v>
       </c>
       <c r="F38">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G38">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H38">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I38">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J38" t="s">
         <v>48</v>
@@ -4666,7 +4666,7 @@
         <v>50</v>
       </c>
       <c r="E39">
-        <v>7.3872000000000021E-2</v>
+        <v>8.8646400000000028E-2</v>
       </c>
       <c r="F39">
         <v>3583</v>
@@ -4722,7 +4722,7 @@
         <v>50</v>
       </c>
       <c r="E40">
-        <v>7.3872000000000021E-2</v>
+        <v>8.8646400000000028E-2</v>
       </c>
       <c r="F40">
         <v>3583</v>
@@ -4778,7 +4778,7 @@
         <v>50</v>
       </c>
       <c r="E41">
-        <v>7.3872000000000021E-2</v>
+        <v>8.8646400000000028E-2</v>
       </c>
       <c r="F41">
         <v>3583</v>
@@ -4834,7 +4834,7 @@
         <v>50</v>
       </c>
       <c r="E42">
-        <v>7.3872000000000021E-2</v>
+        <v>8.8646400000000028E-2</v>
       </c>
       <c r="F42">
         <v>3583</v>
@@ -4890,7 +4890,7 @@
         <v>50</v>
       </c>
       <c r="E43">
-        <v>7.3872000000000021E-2</v>
+        <v>8.8646400000000028E-2</v>
       </c>
       <c r="F43">
         <v>3583</v>
@@ -4946,7 +4946,7 @@
         <v>50</v>
       </c>
       <c r="E44">
-        <v>7.3872000000000021E-2</v>
+        <v>8.8646400000000028E-2</v>
       </c>
       <c r="F44">
         <v>3583</v>
@@ -5002,19 +5002,19 @@
         <v>50</v>
       </c>
       <c r="E45">
-        <v>8.2080000000000042E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F45">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G45">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H45">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I45">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J45" t="s">
         <v>56</v>
@@ -5058,19 +5058,19 @@
         <v>50</v>
       </c>
       <c r="E46">
-        <v>8.2080000000000042E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F46">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G46">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H46">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I46">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J46" t="s">
         <v>57</v>
@@ -5114,19 +5114,19 @@
         <v>50</v>
       </c>
       <c r="E47">
-        <v>8.2080000000000042E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F47">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G47">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H47">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I47">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J47" t="s">
         <v>58</v>
@@ -5170,19 +5170,19 @@
         <v>50</v>
       </c>
       <c r="E48">
-        <v>8.2080000000000042E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F48">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G48">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H48">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I48">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J48" t="s">
         <v>59</v>
@@ -5226,19 +5226,19 @@
         <v>50</v>
       </c>
       <c r="E49">
-        <v>8.2080000000000042E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F49">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G49">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H49">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I49">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J49" t="s">
         <v>60</v>
@@ -5282,19 +5282,19 @@
         <v>50</v>
       </c>
       <c r="E50">
-        <v>8.2080000000000042E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F50">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G50">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H50">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I50">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J50" t="s">
         <v>61</v>
@@ -5338,19 +5338,19 @@
         <v>50</v>
       </c>
       <c r="E51">
-        <v>8.2080000000000042E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F51">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G51">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H51">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I51">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J51" t="s">
         <v>62</v>
@@ -5394,19 +5394,19 @@
         <v>64</v>
       </c>
       <c r="E52">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F52">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G52">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H52">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I52">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J52" t="s">
         <v>63</v>
@@ -5450,19 +5450,19 @@
         <v>64</v>
       </c>
       <c r="E53">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F53">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G53">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H53">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I53">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J53" t="s">
         <v>65</v>
@@ -5506,19 +5506,19 @@
         <v>64</v>
       </c>
       <c r="E54">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F54">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G54">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H54">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I54">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J54" t="s">
         <v>66</v>
@@ -5562,19 +5562,19 @@
         <v>64</v>
       </c>
       <c r="E55">
-        <v>0.23652000000000001</v>
+        <v>0.29665439999999998</v>
       </c>
       <c r="F55">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G55">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H55">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I55">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J55" t="s">
         <v>67</v>
@@ -5618,19 +5618,19 @@
         <v>64</v>
       </c>
       <c r="E56">
-        <v>0.23652000000000001</v>
+        <v>0.29665439999999998</v>
       </c>
       <c r="F56">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G56">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H56">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I56">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J56" t="s">
         <v>68</v>
@@ -5674,19 +5674,19 @@
         <v>64</v>
       </c>
       <c r="E57">
-        <v>0.23652000000000001</v>
+        <v>0.29665439999999998</v>
       </c>
       <c r="F57">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G57">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H57">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I57">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J57" t="s">
         <v>69</v>
@@ -5730,19 +5730,19 @@
         <v>43</v>
       </c>
       <c r="E58">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F58">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G58">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H58">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I58">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J58" t="s">
         <v>70</v>
@@ -5786,19 +5786,19 @@
         <v>43</v>
       </c>
       <c r="E59">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F59">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G59">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H59">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I59">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J59" t="s">
         <v>71</v>
@@ -5842,19 +5842,19 @@
         <v>43</v>
       </c>
       <c r="E60">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F60">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G60">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H60">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I60">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J60" t="s">
         <v>72</v>
@@ -5898,19 +5898,19 @@
         <v>43</v>
       </c>
       <c r="E61">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F61">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G61">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H61">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I61">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J61" t="s">
         <v>73</v>
@@ -5954,19 +5954,19 @@
         <v>43</v>
       </c>
       <c r="E62">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F62">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G62">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H62">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I62">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J62" t="s">
         <v>74</v>
@@ -6010,19 +6010,19 @@
         <v>43</v>
       </c>
       <c r="E63">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F63">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G63">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H63">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I63">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J63" t="s">
         <v>75</v>
@@ -6066,19 +6066,19 @@
         <v>43</v>
       </c>
       <c r="E64">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F64">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G64">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H64">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I64">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J64" t="s">
         <v>76</v>
@@ -6122,19 +6122,19 @@
         <v>43</v>
       </c>
       <c r="E65">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F65">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G65">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H65">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I65">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J65" t="s">
         <v>77</v>
@@ -6178,19 +6178,19 @@
         <v>43</v>
       </c>
       <c r="E66">
-        <v>8.2080000000000014E-2</v>
+        <v>0.13122</v>
       </c>
       <c r="F66">
-        <v>3583</v>
+        <v>3144</v>
       </c>
       <c r="G66">
-        <v>49</v>
+        <v>43.8</v>
       </c>
       <c r="H66">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="I66">
-        <v>0.5605</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J66" t="s">
         <v>78</v>
@@ -6234,19 +6234,19 @@
         <v>80</v>
       </c>
       <c r="E67">
-        <v>0.21236400000000008</v>
+        <v>0.28017360000000002</v>
       </c>
       <c r="F67">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G67">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H67">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I67">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J67" t="s">
         <v>79</v>
@@ -6290,19 +6290,19 @@
         <v>80</v>
       </c>
       <c r="E68">
-        <v>0.21236400000000008</v>
+        <v>0.28017360000000002</v>
       </c>
       <c r="F68">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G68">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H68">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I68">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J68" t="s">
         <v>81</v>
@@ -6346,19 +6346,19 @@
         <v>80</v>
       </c>
       <c r="E69">
-        <v>0.21236400000000008</v>
+        <v>0.28017360000000002</v>
       </c>
       <c r="F69">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G69">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H69">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I69">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J69" t="s">
         <v>82</v>
@@ -6402,19 +6402,19 @@
         <v>80</v>
       </c>
       <c r="E70">
-        <v>0.21236400000000008</v>
+        <v>0.28017360000000002</v>
       </c>
       <c r="F70">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G70">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H70">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I70">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J70" t="s">
         <v>83</v>
@@ -6458,19 +6458,19 @@
         <v>80</v>
       </c>
       <c r="E71">
-        <v>0.21236400000000008</v>
+        <v>0.28017360000000002</v>
       </c>
       <c r="F71">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G71">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H71">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I71">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J71" t="s">
         <v>84</v>
@@ -6514,19 +6514,19 @@
         <v>80</v>
       </c>
       <c r="E72">
-        <v>0.21236400000000008</v>
+        <v>0.28017360000000002</v>
       </c>
       <c r="F72">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G72">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H72">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I72">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J72" t="s">
         <v>85</v>
@@ -6570,19 +6570,19 @@
         <v>87</v>
       </c>
       <c r="E73">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F73">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G73">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H73">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I73">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J73" t="s">
         <v>86</v>
@@ -6626,19 +6626,19 @@
         <v>87</v>
       </c>
       <c r="E74">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F74">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G74">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H74">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I74">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J74" t="s">
         <v>88</v>
@@ -6682,19 +6682,19 @@
         <v>87</v>
       </c>
       <c r="E75">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F75">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G75">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H75">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I75">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J75" t="s">
         <v>89</v>
@@ -6738,19 +6738,19 @@
         <v>87</v>
       </c>
       <c r="E76">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F76">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G76">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H76">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I76">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J76" t="s">
         <v>90</v>
@@ -6794,19 +6794,19 @@
         <v>87</v>
       </c>
       <c r="E77">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F77">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G77">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H77">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I77">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J77" t="s">
         <v>91</v>
@@ -6850,19 +6850,19 @@
         <v>87</v>
       </c>
       <c r="E78">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F78">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G78">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H78">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I78">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J78" t="s">
         <v>92</v>
@@ -6906,19 +6906,19 @@
         <v>94</v>
       </c>
       <c r="E79">
-        <v>0.23652000000000001</v>
+        <v>0.29665439999999993</v>
       </c>
       <c r="F79">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G79">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H79">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I79">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J79" t="s">
         <v>93</v>
@@ -6962,19 +6962,19 @@
         <v>94</v>
       </c>
       <c r="E80">
-        <v>0.23652000000000001</v>
+        <v>0.29665439999999993</v>
       </c>
       <c r="F80">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G80">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H80">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I80">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J80" t="s">
         <v>95</v>
@@ -7018,19 +7018,19 @@
         <v>94</v>
       </c>
       <c r="E81">
-        <v>0.23652000000000001</v>
+        <v>0.29665439999999993</v>
       </c>
       <c r="F81">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G81">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H81">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I81">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J81" t="s">
         <v>96</v>
@@ -7074,19 +7074,19 @@
         <v>94</v>
       </c>
       <c r="E82">
-        <v>0.26729999999999998</v>
+        <v>0.32853599999999999</v>
       </c>
       <c r="F82">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G82">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H82">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I82">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J82" t="s">
         <v>97</v>
@@ -7130,19 +7130,19 @@
         <v>94</v>
       </c>
       <c r="E83">
-        <v>0.26729999999999998</v>
+        <v>0.32853599999999999</v>
       </c>
       <c r="F83">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G83">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H83">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I83">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J83" t="s">
         <v>98</v>
@@ -7186,19 +7186,19 @@
         <v>94</v>
       </c>
       <c r="E84">
-        <v>0.26729999999999998</v>
+        <v>0.32853599999999999</v>
       </c>
       <c r="F84">
-        <v>1923</v>
+        <v>1726</v>
       </c>
       <c r="G84">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="H84">
-        <v>2.88</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="I84">
-        <v>0.80844999999999989</v>
+        <v>0.82269999999999999</v>
       </c>
       <c r="J84" t="s">
         <v>99</v>
@@ -7242,19 +7242,19 @@
         <v>101</v>
       </c>
       <c r="E85">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F85">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G85">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H85">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I85">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J85" t="s">
         <v>100</v>
@@ -7298,19 +7298,19 @@
         <v>101</v>
       </c>
       <c r="E86">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F86">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G86">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H86">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I86">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J86" t="s">
         <v>102</v>
@@ -7354,19 +7354,19 @@
         <v>101</v>
       </c>
       <c r="E87">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F87">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G87">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H87">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I87">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J87" t="s">
         <v>103</v>
@@ -7410,19 +7410,19 @@
         <v>101</v>
       </c>
       <c r="E88">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F88">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G88">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H88">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I88">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J88" t="s">
         <v>104</v>
@@ -7466,19 +7466,19 @@
         <v>101</v>
       </c>
       <c r="E89">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F89">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G89">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H89">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I89">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J89" t="s">
         <v>105</v>
@@ -7522,19 +7522,19 @@
         <v>101</v>
       </c>
       <c r="E90">
-        <v>0.23652000000000001</v>
+        <v>0.29665439999999993</v>
       </c>
       <c r="F90">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G90">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H90">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I90">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J90" t="s">
         <v>106</v>
@@ -7578,19 +7578,19 @@
         <v>108</v>
       </c>
       <c r="E91">
-        <v>0.21236400000000008</v>
+        <v>0.28017360000000002</v>
       </c>
       <c r="F91">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G91">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H91">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I91">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J91" t="s">
         <v>107</v>
@@ -7634,19 +7634,19 @@
         <v>108</v>
       </c>
       <c r="E92">
-        <v>0.21236400000000008</v>
+        <v>0.28017360000000002</v>
       </c>
       <c r="F92">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G92">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H92">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I92">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J92" t="s">
         <v>109</v>
@@ -7690,19 +7690,19 @@
         <v>108</v>
       </c>
       <c r="E93">
-        <v>0.21236400000000008</v>
+        <v>0.28017360000000002</v>
       </c>
       <c r="F93">
-        <v>2445</v>
+        <v>1967</v>
       </c>
       <c r="G93">
-        <v>30.4</v>
+        <v>25.2</v>
       </c>
       <c r="H93">
-        <v>3.52</v>
+        <v>2.73</v>
       </c>
       <c r="I93">
-        <v>0.72770000000000001</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J93" t="s">
         <v>110</v>
@@ -7746,19 +7746,19 @@
         <v>108</v>
       </c>
       <c r="E94">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F94">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G94">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H94">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I94">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J94" t="s">
         <v>111</v>
@@ -7802,19 +7802,19 @@
         <v>108</v>
       </c>
       <c r="E95">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F95">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G95">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H95">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I95">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J95" t="s">
         <v>112</v>
@@ -7858,19 +7858,19 @@
         <v>108</v>
       </c>
       <c r="E96">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F96">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G96">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H96">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I96">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J96" t="s">
         <v>113</v>
@@ -7914,19 +7914,19 @@
         <v>115</v>
       </c>
       <c r="E97">
-        <v>8.7552000000000019E-2</v>
+        <v>0.1707264</v>
       </c>
       <c r="F97">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G97">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H97">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I97">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J97" t="s">
         <v>114</v>
@@ -7970,19 +7970,19 @@
         <v>115</v>
       </c>
       <c r="E98">
-        <v>8.7552000000000019E-2</v>
+        <v>0.1707264</v>
       </c>
       <c r="F98">
-        <v>3583</v>
+        <v>2757</v>
       </c>
       <c r="G98">
-        <v>49</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="H98">
-        <v>4.59</v>
+        <v>3.35</v>
       </c>
       <c r="I98">
-        <v>0.5605</v>
+        <v>0.63080000000000003</v>
       </c>
       <c r="J98" t="s">
         <v>116</v>
@@ -8026,19 +8026,19 @@
         <v>118</v>
       </c>
       <c r="E99">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F99">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G99">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H99">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I99">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J99" t="s">
         <v>117</v>
@@ -8082,19 +8082,19 @@
         <v>118</v>
       </c>
       <c r="E100">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F100">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G100">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H100">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I100">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J100" t="s">
         <v>119</v>
@@ -8138,19 +8138,19 @@
         <v>118</v>
       </c>
       <c r="E101">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F101">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G101">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H101">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I101">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J101" t="s">
         <v>120</v>
@@ -8194,19 +8194,19 @@
         <v>118</v>
       </c>
       <c r="E102">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F102">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G102">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H102">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I102">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J102" t="s">
         <v>121</v>
@@ -8250,19 +8250,19 @@
         <v>118</v>
       </c>
       <c r="E103">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F103">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G103">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H103">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I103">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J103" t="s">
         <v>122</v>
@@ -8306,19 +8306,19 @@
         <v>118</v>
       </c>
       <c r="E104">
-        <v>0.22995000000000002</v>
+        <v>0.288414</v>
       </c>
       <c r="F104">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G104">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H104">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I104">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J104" t="s">
         <v>123</v>
@@ -8362,7 +8362,7 @@
         <v>125</v>
       </c>
       <c r="E105">
-        <v>0.31560749999999999</v>
+        <v>0.37872900000000004</v>
       </c>
       <c r="F105">
         <v>1726</v>
@@ -8418,7 +8418,7 @@
         <v>125</v>
       </c>
       <c r="E106">
-        <v>0.31560749999999999</v>
+        <v>0.37872900000000004</v>
       </c>
       <c r="F106">
         <v>1726</v>
@@ -8474,7 +8474,7 @@
         <v>125</v>
       </c>
       <c r="E107">
-        <v>0.32321250000000001</v>
+        <v>0.38785500000000001</v>
       </c>
       <c r="F107">
         <v>1726</v>
@@ -8530,7 +8530,7 @@
         <v>125</v>
       </c>
       <c r="E108">
-        <v>0.32321250000000001</v>
+        <v>0.38785500000000001</v>
       </c>
       <c r="F108">
         <v>1726</v>
@@ -8586,7 +8586,7 @@
         <v>125</v>
       </c>
       <c r="E109">
-        <v>0.32321250000000001</v>
+        <v>0.38785500000000001</v>
       </c>
       <c r="F109">
         <v>1726</v>
@@ -8642,7 +8642,7 @@
         <v>125</v>
       </c>
       <c r="E110">
-        <v>0.32321250000000001</v>
+        <v>0.38785500000000001</v>
       </c>
       <c r="F110">
         <v>1726</v>
@@ -8698,7 +8698,7 @@
         <v>132</v>
       </c>
       <c r="E111">
-        <v>0.32321250000000001</v>
+        <v>0.38785500000000001</v>
       </c>
       <c r="F111">
         <v>1726</v>
@@ -8754,7 +8754,7 @@
         <v>132</v>
       </c>
       <c r="E112">
-        <v>0.31560749999999999</v>
+        <v>0.37872900000000004</v>
       </c>
       <c r="F112">
         <v>1726</v>
@@ -8810,7 +8810,7 @@
         <v>132</v>
       </c>
       <c r="E113">
-        <v>0.31560749999999999</v>
+        <v>0.37872900000000004</v>
       </c>
       <c r="F113">
         <v>1726</v>
@@ -8866,7 +8866,7 @@
         <v>132</v>
       </c>
       <c r="E114">
-        <v>0.31560749999999999</v>
+        <v>0.37872900000000004</v>
       </c>
       <c r="F114">
         <v>1726</v>
@@ -8922,7 +8922,7 @@
         <v>132</v>
       </c>
       <c r="E115">
-        <v>0.31560749999999999</v>
+        <v>0.37872900000000004</v>
       </c>
       <c r="F115">
         <v>1726</v>
@@ -8978,7 +8978,7 @@
         <v>132</v>
       </c>
       <c r="E116">
-        <v>0.31560749999999999</v>
+        <v>0.37872900000000004</v>
       </c>
       <c r="F116">
         <v>1726</v>
@@ -9034,7 +9034,7 @@
         <v>14</v>
       </c>
       <c r="E117">
-        <v>0.28982625000000001</v>
+        <v>0.37677412500000002</v>
       </c>
       <c r="F117">
         <v>1365</v>
@@ -9090,7 +9090,7 @@
         <v>141</v>
       </c>
       <c r="E118">
-        <v>0.44100000000000006</v>
+        <v>0.57330000000000014</v>
       </c>
       <c r="F118">
         <v>1365</v>
@@ -9146,7 +9146,7 @@
         <v>143</v>
       </c>
       <c r="E119">
-        <v>0.45675000000000004</v>
+        <v>0.59377500000000005</v>
       </c>
       <c r="F119">
         <v>1365</v>
@@ -9202,7 +9202,7 @@
         <v>145</v>
       </c>
       <c r="E120">
-        <v>0.24412500000000001</v>
+        <v>0.31736249999999999</v>
       </c>
       <c r="F120">
         <v>1365</v>
@@ -9258,7 +9258,7 @@
         <v>145</v>
       </c>
       <c r="E121">
-        <v>0.24412500000000001</v>
+        <v>0.31736249999999999</v>
       </c>
       <c r="F121">
         <v>1365</v>
@@ -9314,7 +9314,7 @@
         <v>145</v>
       </c>
       <c r="E122">
-        <v>0.24412500000000001</v>
+        <v>0.31736249999999999</v>
       </c>
       <c r="F122">
         <v>1365</v>
@@ -9370,7 +9370,7 @@
         <v>145</v>
       </c>
       <c r="E123">
-        <v>0.24412500000000001</v>
+        <v>0.31736249999999999</v>
       </c>
       <c r="F123">
         <v>1365</v>
@@ -10490,7 +10490,7 @@
         <v>189</v>
       </c>
       <c r="E143">
-        <v>0.22050000000000003</v>
+        <v>0.28665000000000007</v>
       </c>
       <c r="F143">
         <v>1365</v>
@@ -10546,7 +10546,7 @@
         <v>191</v>
       </c>
       <c r="E144">
-        <v>0.22050000000000003</v>
+        <v>0.28665000000000007</v>
       </c>
       <c r="F144">
         <v>1365</v>
@@ -10602,7 +10602,7 @@
         <v>191</v>
       </c>
       <c r="E145">
-        <v>0.22050000000000003</v>
+        <v>0.28665000000000007</v>
       </c>
       <c r="F145">
         <v>1365</v>
@@ -10658,7 +10658,7 @@
         <v>191</v>
       </c>
       <c r="E146">
-        <v>0.22050000000000003</v>
+        <v>0.28665000000000007</v>
       </c>
       <c r="F146">
         <v>1365</v>
@@ -10714,7 +10714,7 @@
         <v>191</v>
       </c>
       <c r="E147">
-        <v>0.22050000000000003</v>
+        <v>0.28665000000000007</v>
       </c>
       <c r="F147">
         <v>1365</v>
@@ -10770,7 +10770,7 @@
         <v>191</v>
       </c>
       <c r="E148">
-        <v>0.22050000000000003</v>
+        <v>0.28665000000000007</v>
       </c>
       <c r="F148">
         <v>1365</v>
@@ -10826,7 +10826,7 @@
         <v>197</v>
       </c>
       <c r="E149">
-        <v>0.17325000000000002</v>
+        <v>0.22522500000000001</v>
       </c>
       <c r="F149">
         <v>1365</v>
@@ -10882,7 +10882,7 @@
         <v>197</v>
       </c>
       <c r="E150">
-        <v>0.17325000000000002</v>
+        <v>0.22522500000000001</v>
       </c>
       <c r="F150">
         <v>1365</v>
@@ -10938,7 +10938,7 @@
         <v>197</v>
       </c>
       <c r="E151">
-        <v>0.17325000000000002</v>
+        <v>0.22522500000000001</v>
       </c>
       <c r="F151">
         <v>1365</v>
@@ -10994,7 +10994,7 @@
         <v>201</v>
       </c>
       <c r="E152">
-        <v>0.17325000000000002</v>
+        <v>0.22522500000000001</v>
       </c>
       <c r="F152">
         <v>1365</v>
@@ -11050,7 +11050,7 @@
         <v>201</v>
       </c>
       <c r="E153">
-        <v>0.17325000000000002</v>
+        <v>0.22522500000000001</v>
       </c>
       <c r="F153">
         <v>1365</v>
@@ -11106,7 +11106,7 @@
         <v>201</v>
       </c>
       <c r="E154">
-        <v>0.17325000000000002</v>
+        <v>0.22522500000000001</v>
       </c>
       <c r="F154">
         <v>1365</v>
@@ -11162,7 +11162,7 @@
         <v>189</v>
       </c>
       <c r="E155">
-        <v>0.22050000000000003</v>
+        <v>0.28665000000000007</v>
       </c>
       <c r="F155">
         <v>1365</v>
@@ -11218,7 +11218,7 @@
         <v>189</v>
       </c>
       <c r="E156">
-        <v>0.22050000000000003</v>
+        <v>0.28665000000000007</v>
       </c>
       <c r="F156">
         <v>1365</v>
@@ -11274,7 +11274,7 @@
         <v>189</v>
       </c>
       <c r="E157">
-        <v>0.22050000000000003</v>
+        <v>0.28665000000000007</v>
       </c>
       <c r="F157">
         <v>1365</v>
@@ -11330,7 +11330,7 @@
         <v>189</v>
       </c>
       <c r="E158">
-        <v>0.22050000000000003</v>
+        <v>0.28665000000000007</v>
       </c>
       <c r="F158">
         <v>1365</v>
@@ -11386,7 +11386,7 @@
         <v>189</v>
       </c>
       <c r="E159">
-        <v>0.22050000000000003</v>
+        <v>0.28665000000000007</v>
       </c>
       <c r="F159">
         <v>1365</v>
@@ -11442,7 +11442,7 @@
         <v>189</v>
       </c>
       <c r="E160">
-        <v>0.22050000000000003</v>
+        <v>0.28665000000000007</v>
       </c>
       <c r="F160">
         <v>1365</v>
@@ -11498,7 +11498,7 @@
         <v>189</v>
       </c>
       <c r="E161">
-        <v>0.22050000000000003</v>
+        <v>0.28665000000000007</v>
       </c>
       <c r="F161">
         <v>1365</v>
@@ -11554,7 +11554,7 @@
         <v>189</v>
       </c>
       <c r="E162">
-        <v>0.22050000000000003</v>
+        <v>0.28665000000000007</v>
       </c>
       <c r="F162">
         <v>1365</v>
@@ -11605,7 +11605,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{637C4294-6219-47B6-875D-9B6C703ACB2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1AF831A-BFEE-4FD9-84A9-7079DEAC8D3D}">
   <dimension ref="B9:T57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14245,7 +14245,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC2BE351-2F20-4594-B8B9-F0ACF530363A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6F432BB-0B2A-443E-945A-C86FA75EE2DE}">
   <dimension ref="B9:T313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14330,7 +14330,7 @@
         <v>0.264685</v>
       </c>
       <c r="G11">
-        <v>0.29700000000000004</v>
+        <v>0.35640000000000005</v>
       </c>
       <c r="H11">
         <v>3421.2499999999995</v>
@@ -14383,7 +14383,7 @@
         <v>0.37</v>
       </c>
       <c r="G12">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H12">
         <v>1700</v>
@@ -14436,7 +14436,7 @@
         <v>0.39</v>
       </c>
       <c r="G13">
-        <v>0.30600000000000005</v>
+        <v>0.36719999999999997</v>
       </c>
       <c r="H13">
         <v>1700</v>
@@ -14489,7 +14489,7 @@
         <v>0.39600000000000002</v>
       </c>
       <c r="G14">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H14">
         <v>1700</v>
@@ -14542,7 +14542,7 @@
         <v>0.39600000000000002</v>
       </c>
       <c r="G15">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H15">
         <v>1700</v>
@@ -14595,7 +14595,7 @@
         <v>0.4</v>
       </c>
       <c r="G16">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000008</v>
       </c>
       <c r="H16">
         <v>1700</v>
@@ -14648,7 +14648,7 @@
         <v>0.4</v>
       </c>
       <c r="G17">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000008</v>
       </c>
       <c r="H17">
         <v>1700</v>
@@ -14701,7 +14701,7 @@
         <v>0.2</v>
       </c>
       <c r="G18">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H18">
         <v>1955</v>
@@ -14754,7 +14754,7 @@
         <v>0.2</v>
       </c>
       <c r="G19">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H19">
         <v>1955</v>
@@ -14807,7 +14807,7 @@
         <v>0.2</v>
       </c>
       <c r="G20">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H20">
         <v>1955</v>
@@ -14860,7 +14860,7 @@
         <v>0.2</v>
       </c>
       <c r="G21">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H21">
         <v>1955</v>
@@ -14913,7 +14913,7 @@
         <v>0.2</v>
       </c>
       <c r="G22">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H22">
         <v>1955</v>
@@ -14966,7 +14966,7 @@
         <v>0.2</v>
       </c>
       <c r="G23">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H23">
         <v>1955</v>
@@ -15019,7 +15019,7 @@
         <v>0.2</v>
       </c>
       <c r="G24">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H24">
         <v>1955</v>
@@ -15072,7 +15072,7 @@
         <v>0.2</v>
       </c>
       <c r="G25">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H25">
         <v>1955</v>
@@ -15125,7 +15125,7 @@
         <v>0.6</v>
       </c>
       <c r="G26">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H26">
         <v>1700</v>
@@ -15178,7 +15178,7 @@
         <v>0.6</v>
       </c>
       <c r="G27">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H27">
         <v>1700</v>
@@ -15231,7 +15231,7 @@
         <v>0.6</v>
       </c>
       <c r="G28">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H28">
         <v>1700</v>
@@ -15284,7 +15284,7 @@
         <v>0.6</v>
       </c>
       <c r="G29">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H29">
         <v>1700</v>
@@ -15337,7 +15337,7 @@
         <v>0.6</v>
       </c>
       <c r="G30">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H30">
         <v>1700</v>
@@ -15390,7 +15390,7 @@
         <v>0.2</v>
       </c>
       <c r="G31">
-        <v>0.28800000000000003</v>
+        <v>0.34560000000000002</v>
       </c>
       <c r="H31">
         <v>1955</v>
@@ -15443,7 +15443,7 @@
         <v>0.2</v>
       </c>
       <c r="G32">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H32">
         <v>1955</v>
@@ -15496,7 +15496,7 @@
         <v>0.2</v>
       </c>
       <c r="G33">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H33">
         <v>1955</v>
@@ -15549,7 +15549,7 @@
         <v>0.2</v>
       </c>
       <c r="G34">
-        <v>0.28800000000000003</v>
+        <v>0.34560000000000002</v>
       </c>
       <c r="H34">
         <v>1955</v>
@@ -15602,7 +15602,7 @@
         <v>0.2</v>
       </c>
       <c r="G35">
-        <v>0.28800000000000003</v>
+        <v>0.34560000000000002</v>
       </c>
       <c r="H35">
         <v>1955</v>
@@ -15655,7 +15655,7 @@
         <v>0.2</v>
       </c>
       <c r="G36">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H36">
         <v>1955</v>
@@ -15708,7 +15708,7 @@
         <v>0.2</v>
       </c>
       <c r="G37">
-        <v>0.28800000000000003</v>
+        <v>0.34560000000000002</v>
       </c>
       <c r="H37">
         <v>1955</v>
@@ -15761,7 +15761,7 @@
         <v>0.2</v>
       </c>
       <c r="G38">
-        <v>0.28800000000000003</v>
+        <v>0.34560000000000002</v>
       </c>
       <c r="H38">
         <v>1955</v>
@@ -15814,7 +15814,7 @@
         <v>0.2</v>
       </c>
       <c r="G39">
-        <v>0.28800000000000003</v>
+        <v>0.34560000000000002</v>
       </c>
       <c r="H39">
         <v>1955</v>
@@ -15867,7 +15867,7 @@
         <v>0.03</v>
       </c>
       <c r="G40">
-        <v>0.24300000000000002</v>
+        <v>0.29160000000000003</v>
       </c>
       <c r="H40">
         <v>2295</v>
@@ -15920,7 +15920,7 @@
         <v>0.03</v>
       </c>
       <c r="G41">
-        <v>0.24300000000000002</v>
+        <v>0.29160000000000003</v>
       </c>
       <c r="H41">
         <v>2295</v>
@@ -15973,7 +15973,7 @@
         <v>0.03</v>
       </c>
       <c r="G42">
-        <v>0.24300000000000002</v>
+        <v>0.29160000000000003</v>
       </c>
       <c r="H42">
         <v>2295</v>
@@ -16026,7 +16026,7 @@
         <v>0.03</v>
       </c>
       <c r="G43">
-        <v>0.24300000000000002</v>
+        <v>0.29160000000000003</v>
       </c>
       <c r="H43">
         <v>2295</v>
@@ -16079,7 +16079,7 @@
         <v>0.03</v>
       </c>
       <c r="G44">
-        <v>0.24300000000000002</v>
+        <v>0.29160000000000003</v>
       </c>
       <c r="H44">
         <v>2295</v>
@@ -16132,7 +16132,7 @@
         <v>0.03</v>
       </c>
       <c r="G45">
-        <v>0.24300000000000002</v>
+        <v>0.29160000000000003</v>
       </c>
       <c r="H45">
         <v>2295</v>
@@ -16185,7 +16185,7 @@
         <v>0.06</v>
       </c>
       <c r="G46">
-        <v>0.27000000000000007</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H46">
         <v>1955</v>
@@ -16238,7 +16238,7 @@
         <v>0.06</v>
       </c>
       <c r="G47">
-        <v>0.27000000000000007</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H47">
         <v>1955</v>
@@ -16291,7 +16291,7 @@
         <v>0.06</v>
       </c>
       <c r="G48">
-        <v>0.27000000000000007</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H48">
         <v>1955</v>
@@ -16344,7 +16344,7 @@
         <v>0.06</v>
       </c>
       <c r="G49">
-        <v>0.27000000000000007</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H49">
         <v>1955</v>
@@ -16397,7 +16397,7 @@
         <v>0.06</v>
       </c>
       <c r="G50">
-        <v>0.27000000000000007</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H50">
         <v>1955</v>
@@ -16450,7 +16450,7 @@
         <v>0.06</v>
       </c>
       <c r="G51">
-        <v>0.27000000000000007</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H51">
         <v>1955</v>
@@ -16503,7 +16503,7 @@
         <v>0.06</v>
       </c>
       <c r="G52">
-        <v>0.27000000000000007</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H52">
         <v>1955</v>
@@ -16556,7 +16556,7 @@
         <v>0.68600000000000005</v>
       </c>
       <c r="G53">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H53">
         <v>1700</v>
@@ -16609,7 +16609,7 @@
         <v>0.68600000000000005</v>
       </c>
       <c r="G54">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H54">
         <v>1700</v>
@@ -16662,7 +16662,7 @@
         <v>0.68600000000000005</v>
       </c>
       <c r="G55">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H55">
         <v>1700</v>
@@ -16715,7 +16715,7 @@
         <v>0.68600000000000005</v>
       </c>
       <c r="G56">
-        <v>0.32400000000000001</v>
+        <v>0.38879999999999998</v>
       </c>
       <c r="H56">
         <v>1700</v>
@@ -16768,7 +16768,7 @@
         <v>0.68600000000000005</v>
       </c>
       <c r="G57">
-        <v>0.32400000000000001</v>
+        <v>0.38879999999999998</v>
       </c>
       <c r="H57">
         <v>1700</v>
@@ -16821,7 +16821,7 @@
         <v>0.68600000000000005</v>
       </c>
       <c r="G58">
-        <v>0.32400000000000001</v>
+        <v>0.38879999999999998</v>
       </c>
       <c r="H58">
         <v>1700</v>
@@ -16874,7 +16874,7 @@
         <v>0.1</v>
       </c>
       <c r="G59">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H59">
         <v>1955</v>
@@ -16927,7 +16927,7 @@
         <v>0.1</v>
       </c>
       <c r="G60">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H60">
         <v>1955</v>
@@ -16980,7 +16980,7 @@
         <v>0.1</v>
       </c>
       <c r="G61">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H61">
         <v>1955</v>
@@ -17033,7 +17033,7 @@
         <v>0.1</v>
       </c>
       <c r="G62">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H62">
         <v>1955</v>
@@ -17086,7 +17086,7 @@
         <v>0.1</v>
       </c>
       <c r="G63">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H63">
         <v>1955</v>
@@ -17139,7 +17139,7 @@
         <v>0.125</v>
       </c>
       <c r="G64">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H64">
         <v>1955</v>
@@ -17192,7 +17192,7 @@
         <v>0.125</v>
       </c>
       <c r="G65">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H65">
         <v>1955</v>
@@ -17245,7 +17245,7 @@
         <v>0.125</v>
       </c>
       <c r="G66">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H66">
         <v>1955</v>
@@ -17298,7 +17298,7 @@
         <v>0.125</v>
       </c>
       <c r="G67">
-        <v>0.27</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="H67">
         <v>1955</v>
@@ -17351,7 +17351,7 @@
         <v>0.5</v>
       </c>
       <c r="G68">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H68">
         <v>1700</v>
@@ -17404,7 +17404,7 @@
         <v>0.5</v>
       </c>
       <c r="G69">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H69">
         <v>1700</v>
@@ -17457,7 +17457,7 @@
         <v>0.5</v>
       </c>
       <c r="G70">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H70">
         <v>1700</v>
@@ -17510,7 +17510,7 @@
         <v>0.5</v>
       </c>
       <c r="G71">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H71">
         <v>1700</v>
@@ -17563,7 +17563,7 @@
         <v>0.5</v>
       </c>
       <c r="G72">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H72">
         <v>1700</v>
@@ -17616,7 +17616,7 @@
         <v>0.5</v>
       </c>
       <c r="G73">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H73">
         <v>1700</v>
@@ -17669,7 +17669,7 @@
         <v>0.61799999999999999</v>
       </c>
       <c r="G74">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H74">
         <v>1700</v>
@@ -17722,7 +17722,7 @@
         <v>0.61799999999999999</v>
       </c>
       <c r="G75">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H75">
         <v>1700</v>
@@ -17775,7 +17775,7 @@
         <v>0.61799999999999999</v>
       </c>
       <c r="G76">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H76">
         <v>1700</v>
@@ -17828,7 +17828,7 @@
         <v>0.61799999999999999</v>
       </c>
       <c r="G77">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H77">
         <v>1700</v>
@@ -17881,7 +17881,7 @@
         <v>0.61799999999999999</v>
       </c>
       <c r="G78">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H78">
         <v>1700</v>
@@ -17934,7 +17934,7 @@
         <v>0.61799999999999999</v>
       </c>
       <c r="G79">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H79">
         <v>1700</v>
@@ -17987,7 +17987,7 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="G80">
-        <v>0.32400000000000001</v>
+        <v>0.38879999999999992</v>
       </c>
       <c r="H80">
         <v>1700</v>
@@ -18040,7 +18040,7 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="G81">
-        <v>0.32400000000000001</v>
+        <v>0.38879999999999992</v>
       </c>
       <c r="H81">
         <v>1700</v>
@@ -18093,7 +18093,7 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="G82">
-        <v>0.32400000000000001</v>
+        <v>0.38879999999999992</v>
       </c>
       <c r="H82">
         <v>1700</v>
@@ -18146,7 +18146,7 @@
         <v>0.71599999999999997</v>
       </c>
       <c r="G83">
-        <v>0.32400000000000001</v>
+        <v>0.38879999999999998</v>
       </c>
       <c r="H83">
         <v>1700</v>
@@ -18199,7 +18199,7 @@
         <v>0.71599999999999997</v>
       </c>
       <c r="G84">
-        <v>0.32400000000000001</v>
+        <v>0.38879999999999998</v>
       </c>
       <c r="H84">
         <v>1700</v>
@@ -18252,7 +18252,7 @@
         <v>0.71599999999999997</v>
       </c>
       <c r="G85">
-        <v>0.32400000000000001</v>
+        <v>0.38879999999999998</v>
       </c>
       <c r="H85">
         <v>1700</v>
@@ -18305,7 +18305,7 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="G86">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H86">
         <v>1700</v>
@@ -18358,7 +18358,7 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="G87">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H87">
         <v>1700</v>
@@ -18411,7 +18411,7 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="G88">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H88">
         <v>1700</v>
@@ -18464,7 +18464,7 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="G89">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H89">
         <v>1700</v>
@@ -18517,7 +18517,7 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="G90">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H90">
         <v>1700</v>
@@ -18570,7 +18570,7 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="G91">
-        <v>0.32400000000000001</v>
+        <v>0.38879999999999992</v>
       </c>
       <c r="H91">
         <v>1700</v>
@@ -18623,7 +18623,7 @@
         <v>0.6</v>
       </c>
       <c r="G92">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H92">
         <v>1700</v>
@@ -18676,7 +18676,7 @@
         <v>0.6</v>
       </c>
       <c r="G93">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H93">
         <v>1700</v>
@@ -18729,7 +18729,7 @@
         <v>0.6</v>
       </c>
       <c r="G94">
-        <v>0.30600000000000005</v>
+        <v>0.36720000000000003</v>
       </c>
       <c r="H94">
         <v>1700</v>
@@ -18782,7 +18782,7 @@
         <v>0.6</v>
       </c>
       <c r="G95">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H95">
         <v>1700</v>
@@ -18835,7 +18835,7 @@
         <v>0.6</v>
       </c>
       <c r="G96">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H96">
         <v>1700</v>
@@ -18888,7 +18888,7 @@
         <v>0.6</v>
       </c>
       <c r="G97">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H97">
         <v>1700</v>
@@ -18941,7 +18941,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="G98">
-        <v>0.28800000000000003</v>
+        <v>0.34560000000000002</v>
       </c>
       <c r="H98">
         <v>2295</v>
@@ -18994,7 +18994,7 @@
         <v>3.4299999999999997E-2</v>
       </c>
       <c r="G99">
-        <v>0.28800000000000003</v>
+        <v>0.34560000000000002</v>
       </c>
       <c r="H99">
         <v>2295</v>
@@ -19047,7 +19047,7 @@
         <v>0.60899999999999999</v>
       </c>
       <c r="G100">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H100">
         <v>1700</v>
@@ -19100,7 +19100,7 @@
         <v>0.60899999999999999</v>
       </c>
       <c r="G101">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H101">
         <v>1700</v>
@@ -19153,7 +19153,7 @@
         <v>0.60899999999999999</v>
       </c>
       <c r="G102">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H102">
         <v>1700</v>
@@ -19206,7 +19206,7 @@
         <v>0.60899999999999999</v>
       </c>
       <c r="G103">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H103">
         <v>1700</v>
@@ -19259,7 +19259,7 @@
         <v>0.60899999999999999</v>
       </c>
       <c r="G104">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H104">
         <v>1700</v>
@@ -19312,7 +19312,7 @@
         <v>0.60899999999999999</v>
       </c>
       <c r="G105">
-        <v>0.315</v>
+        <v>0.378</v>
       </c>
       <c r="H105">
         <v>1700</v>
@@ -19365,7 +19365,7 @@
         <v>0.8</v>
       </c>
       <c r="G106">
-        <v>0.3735</v>
+        <v>0.44819999999999999</v>
       </c>
       <c r="H106">
         <v>1870</v>
@@ -19418,7 +19418,7 @@
         <v>0.8</v>
       </c>
       <c r="G107">
-        <v>0.3735</v>
+        <v>0.44819999999999999</v>
       </c>
       <c r="H107">
         <v>1870</v>
@@ -19471,7 +19471,7 @@
         <v>0.8</v>
       </c>
       <c r="G108">
-        <v>0.38250000000000001</v>
+        <v>0.45899999999999996</v>
       </c>
       <c r="H108">
         <v>1870</v>
@@ -19524,7 +19524,7 @@
         <v>0.8</v>
       </c>
       <c r="G109">
-        <v>0.38250000000000001</v>
+        <v>0.45899999999999996</v>
       </c>
       <c r="H109">
         <v>1870</v>
@@ -19577,7 +19577,7 @@
         <v>0.8</v>
       </c>
       <c r="G110">
-        <v>0.38250000000000001</v>
+        <v>0.45899999999999996</v>
       </c>
       <c r="H110">
         <v>1870</v>
@@ -19630,7 +19630,7 @@
         <v>0.8</v>
       </c>
       <c r="G111">
-        <v>0.38250000000000001</v>
+        <v>0.45899999999999996</v>
       </c>
       <c r="H111">
         <v>1870</v>
@@ -19683,7 +19683,7 @@
         <v>0.79479999999999995</v>
       </c>
       <c r="G112">
-        <v>0.38250000000000001</v>
+        <v>0.45899999999999996</v>
       </c>
       <c r="H112">
         <v>1870</v>
@@ -19736,7 +19736,7 @@
         <v>0.79479999999999995</v>
       </c>
       <c r="G113">
-        <v>0.3735</v>
+        <v>0.44819999999999999</v>
       </c>
       <c r="H113">
         <v>1870</v>
@@ -19789,7 +19789,7 @@
         <v>0.79479999999999995</v>
       </c>
       <c r="G114">
-        <v>0.3735</v>
+        <v>0.44819999999999999</v>
       </c>
       <c r="H114">
         <v>1870</v>
@@ -19842,7 +19842,7 @@
         <v>0.79479999999999995</v>
       </c>
       <c r="G115">
-        <v>0.3735</v>
+        <v>0.44819999999999999</v>
       </c>
       <c r="H115">
         <v>1870</v>
@@ -19895,7 +19895,7 @@
         <v>0.79479999999999995</v>
       </c>
       <c r="G116">
-        <v>0.3735</v>
+        <v>0.44819999999999999</v>
       </c>
       <c r="H116">
         <v>1870</v>
@@ -19948,7 +19948,7 @@
         <v>0.79479999999999995</v>
       </c>
       <c r="G117">
-        <v>0.3735</v>
+        <v>0.44819999999999999</v>
       </c>
       <c r="H117">
         <v>1870</v>
@@ -20001,7 +20001,7 @@
         <v>5.0000000000001155E-3</v>
       </c>
       <c r="G118">
-        <v>0.33123000000000002</v>
+        <v>0.43059900000000007</v>
       </c>
       <c r="K118">
         <v>33</v>
@@ -20045,7 +20045,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="G119">
-        <v>0.50400000000000011</v>
+        <v>0.65520000000000023</v>
       </c>
       <c r="H119">
         <v>977.5</v>
@@ -20098,7 +20098,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="G120">
-        <v>0.52200000000000002</v>
+        <v>0.67860000000000009</v>
       </c>
       <c r="H120">
         <v>850</v>
@@ -20151,7 +20151,7 @@
         <v>0.16750000000000001</v>
       </c>
       <c r="G121">
-        <v>0.27900000000000003</v>
+        <v>0.36270000000000002</v>
       </c>
       <c r="H121">
         <v>781.99999999999989</v>
@@ -20204,7 +20204,7 @@
         <v>0.16750000000000001</v>
       </c>
       <c r="G122">
-        <v>0.27900000000000003</v>
+        <v>0.36270000000000002</v>
       </c>
       <c r="H122">
         <v>781.99999999999989</v>
@@ -20257,7 +20257,7 @@
         <v>0.16750000000000001</v>
       </c>
       <c r="G123">
-        <v>0.27900000000000003</v>
+        <v>0.36270000000000002</v>
       </c>
       <c r="H123">
         <v>781.99999999999989</v>
@@ -20310,7 +20310,7 @@
         <v>0.16750000000000001</v>
       </c>
       <c r="G124">
-        <v>0.27900000000000003</v>
+        <v>0.36270000000000002</v>
       </c>
       <c r="H124">
         <v>781.99999999999989</v>
@@ -21835,7 +21835,7 @@
         <v>0.1492</v>
       </c>
       <c r="G153">
-        <v>0.25200000000000006</v>
+        <v>0.32760000000000011</v>
       </c>
       <c r="H153">
         <v>879.75</v>
@@ -21888,7 +21888,7 @@
         <v>0.14799999999999999</v>
       </c>
       <c r="G154">
-        <v>0.25200000000000006</v>
+        <v>0.32760000000000011</v>
       </c>
       <c r="H154">
         <v>879.75</v>
@@ -21941,7 +21941,7 @@
         <v>0.14799999999999999</v>
       </c>
       <c r="G155">
-        <v>0.25200000000000006</v>
+        <v>0.32760000000000011</v>
       </c>
       <c r="H155">
         <v>879.75</v>
@@ -21994,7 +21994,7 @@
         <v>0.14799999999999999</v>
       </c>
       <c r="G156">
-        <v>0.25200000000000006</v>
+        <v>0.32760000000000011</v>
       </c>
       <c r="H156">
         <v>879.75</v>
@@ -22047,7 +22047,7 @@
         <v>0.14799999999999999</v>
       </c>
       <c r="G157">
-        <v>0.25200000000000006</v>
+        <v>0.32760000000000011</v>
       </c>
       <c r="H157">
         <v>879.75</v>
@@ -22100,7 +22100,7 @@
         <v>0.14799999999999999</v>
       </c>
       <c r="G158">
-        <v>0.25200000000000006</v>
+        <v>0.32760000000000011</v>
       </c>
       <c r="H158">
         <v>879.75</v>
@@ -22153,7 +22153,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G159">
-        <v>0.19800000000000004</v>
+        <v>0.25740000000000002</v>
       </c>
       <c r="H159">
         <v>879.75</v>
@@ -22206,7 +22206,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G160">
-        <v>0.19800000000000004</v>
+        <v>0.25740000000000002</v>
       </c>
       <c r="H160">
         <v>879.75</v>
@@ -22259,7 +22259,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G161">
-        <v>0.19800000000000004</v>
+        <v>0.25740000000000002</v>
       </c>
       <c r="H161">
         <v>879.75</v>
@@ -22312,7 +22312,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G162">
-        <v>0.19800000000000004</v>
+        <v>0.25740000000000002</v>
       </c>
       <c r="H162">
         <v>879.75</v>
@@ -22365,7 +22365,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G163">
-        <v>0.19800000000000004</v>
+        <v>0.25740000000000002</v>
       </c>
       <c r="H163">
         <v>879.75</v>
@@ -22418,7 +22418,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G164">
-        <v>0.19800000000000004</v>
+        <v>0.25740000000000002</v>
       </c>
       <c r="H164">
         <v>879.75</v>
@@ -22471,7 +22471,7 @@
         <v>0.14830000000000002</v>
       </c>
       <c r="G165">
-        <v>0.25200000000000006</v>
+        <v>0.32760000000000011</v>
       </c>
       <c r="H165">
         <v>879.75</v>
@@ -22524,7 +22524,7 @@
         <v>0.14830000000000002</v>
       </c>
       <c r="G166">
-        <v>0.25200000000000006</v>
+        <v>0.32760000000000011</v>
       </c>
       <c r="H166">
         <v>879.75</v>
@@ -22577,7 +22577,7 @@
         <v>0.14830000000000002</v>
       </c>
       <c r="G167">
-        <v>0.25200000000000006</v>
+        <v>0.32760000000000011</v>
       </c>
       <c r="H167">
         <v>879.75</v>
@@ -22630,7 +22630,7 @@
         <v>0.14830000000000002</v>
       </c>
       <c r="G168">
-        <v>0.25200000000000006</v>
+        <v>0.32760000000000011</v>
       </c>
       <c r="H168">
         <v>879.75</v>
@@ -22683,7 +22683,7 @@
         <v>0.14830000000000002</v>
       </c>
       <c r="G169">
-        <v>0.25200000000000006</v>
+        <v>0.32760000000000011</v>
       </c>
       <c r="H169">
         <v>879.75</v>
@@ -22736,7 +22736,7 @@
         <v>0.1492</v>
       </c>
       <c r="G170">
-        <v>0.25200000000000006</v>
+        <v>0.32760000000000011</v>
       </c>
       <c r="H170">
         <v>879.75</v>
@@ -22789,7 +22789,7 @@
         <v>0.1492</v>
       </c>
       <c r="G171">
-        <v>0.25200000000000006</v>
+        <v>0.32760000000000011</v>
       </c>
       <c r="H171">
         <v>879.75</v>
@@ -22842,7 +22842,7 @@
         <v>0.1492</v>
       </c>
       <c r="G172">
-        <v>0.25200000000000006</v>
+        <v>0.32760000000000011</v>
       </c>
       <c r="H172">
         <v>879.75</v>
@@ -22901,7 +22901,7 @@
         <v>33</v>
       </c>
       <c r="L173">
-        <v>0.24176079764715144</v>
+        <v>0.24176079764715142</v>
       </c>
       <c r="N173" t="s">
         <v>309</v>
@@ -22948,7 +22948,7 @@
         <v>33</v>
       </c>
       <c r="L174">
-        <v>0.24176079764715144</v>
+        <v>0.24176079764715142</v>
       </c>
       <c r="N174" t="s">
         <v>309</v>
@@ -22995,7 +22995,7 @@
         <v>33</v>
       </c>
       <c r="L175">
-        <v>0.24176079764715144</v>
+        <v>0.24176079764715142</v>
       </c>
       <c r="N175" t="s">
         <v>309</v>
@@ -23228,7 +23228,7 @@
         <v>222</v>
       </c>
       <c r="P179" t="s">
-        <v>422</v>
+        <v>482</v>
       </c>
       <c r="Q179" t="s">
         <v>311</v>
@@ -23284,7 +23284,7 @@
         <v>222</v>
       </c>
       <c r="P180" t="s">
-        <v>482</v>
+        <v>422</v>
       </c>
       <c r="Q180" t="s">
         <v>311</v>
@@ -23676,7 +23676,7 @@
         <v>232</v>
       </c>
       <c r="P187" t="s">
-        <v>422</v>
+        <v>482</v>
       </c>
       <c r="Q187" t="s">
         <v>311</v>
@@ -23732,7 +23732,7 @@
         <v>232</v>
       </c>
       <c r="P188" t="s">
-        <v>482</v>
+        <v>422</v>
       </c>
       <c r="Q188" t="s">
         <v>311</v>
@@ -24684,7 +24684,7 @@
         <v>264</v>
       </c>
       <c r="P205" t="s">
-        <v>422</v>
+        <v>482</v>
       </c>
       <c r="Q205" t="s">
         <v>311</v>
@@ -24740,7 +24740,7 @@
         <v>264</v>
       </c>
       <c r="P206" t="s">
-        <v>482</v>
+        <v>422</v>
       </c>
       <c r="Q206" t="s">
         <v>311</v>
@@ -25188,7 +25188,7 @@
         <v>275</v>
       </c>
       <c r="P214" t="s">
-        <v>422</v>
+        <v>482</v>
       </c>
       <c r="Q214" t="s">
         <v>311</v>
@@ -25244,7 +25244,7 @@
         <v>275</v>
       </c>
       <c r="P215" t="s">
-        <v>482</v>
+        <v>422</v>
       </c>
       <c r="Q215" t="s">
         <v>311</v>
@@ -29031,7 +29031,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C49352-9198-4229-9227-513B0F34409C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1996E650-4E64-450B-B2DC-E9BEEC7AB7BD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
+++ b/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1435708-DD85-44BE-869E-E0D29E2B632F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{80F62DD9-B96B-4164-BD0F-B77D60C02DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EE5EA15E-C6B9-494F-8899-E53BDADD03F7}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{818AFC5D-4348-4DAB-9327-FF00DA2B2DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3019,7 +3019,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40F67264-4228-432E-9A8F-272BC368444F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68486C5C-D8AF-4288-A119-327A67E0B554}">
   <dimension ref="B9:T162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11605,7 +11605,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1AF831A-BFEE-4FD9-84A9-7079DEAC8D3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB0AE9F-8256-41E9-9940-DDC948289F0A}">
   <dimension ref="B9:T57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14245,7 +14245,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6F432BB-0B2A-443E-945A-C86FA75EE2DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F320A231-1972-4D02-9D83-090BE24DA54B}">
   <dimension ref="B9:T313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23116,7 +23116,7 @@
         <v>221</v>
       </c>
       <c r="P177" t="s">
-        <v>482</v>
+        <v>422</v>
       </c>
       <c r="Q177" t="s">
         <v>311</v>
@@ -23172,7 +23172,7 @@
         <v>221</v>
       </c>
       <c r="P178" t="s">
-        <v>422</v>
+        <v>482</v>
       </c>
       <c r="Q178" t="s">
         <v>311</v>
@@ -23676,7 +23676,7 @@
         <v>232</v>
       </c>
       <c r="P187" t="s">
-        <v>482</v>
+        <v>422</v>
       </c>
       <c r="Q187" t="s">
         <v>311</v>
@@ -23732,7 +23732,7 @@
         <v>232</v>
       </c>
       <c r="P188" t="s">
-        <v>422</v>
+        <v>482</v>
       </c>
       <c r="Q188" t="s">
         <v>311</v>
@@ -25300,7 +25300,7 @@
         <v>278</v>
       </c>
       <c r="P216" t="s">
-        <v>422</v>
+        <v>482</v>
       </c>
       <c r="Q216" t="s">
         <v>311</v>
@@ -25356,7 +25356,7 @@
         <v>278</v>
       </c>
       <c r="P217" t="s">
-        <v>482</v>
+        <v>422</v>
       </c>
       <c r="Q217" t="s">
         <v>311</v>
@@ -25916,7 +25916,7 @@
         <v>296</v>
       </c>
       <c r="P227" t="s">
-        <v>422</v>
+        <v>482</v>
       </c>
       <c r="Q227" t="s">
         <v>311</v>
@@ -25972,7 +25972,7 @@
         <v>296</v>
       </c>
       <c r="P228" t="s">
-        <v>482</v>
+        <v>422</v>
       </c>
       <c r="Q228" t="s">
         <v>311</v>
@@ -29031,7 +29031,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1996E650-4E64-450B-B2DC-E9BEEC7AB7BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10CDE905-E37C-4D10-9700-2E4E6440AE57}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
+++ b/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AAD5050-4014-4354-8AB2-E72DC662C2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E86660C-E27F-4C5D-BBF8-5A48FBDEFA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6423D655-1868-41DF-88D3-36C3F19C4FAB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{45177100-C8EE-494F-9509-F27232C67BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3028,7 +3028,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0633886-4B64-404E-86B8-333BA2810E8A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0D3EAA-BF38-4F9F-9345-C279A348BCB2}">
   <dimension ref="B9:V162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12532,7 +12532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D360010-9D64-4AD0-842E-37D7A7D601BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{893800B3-8B03-40C2-8796-36AB201097D6}">
   <dimension ref="B9:V57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15457,7 +15457,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D75172B-78F8-49BD-B992-BDF37B8BCF84}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{274FF8A8-B03A-4CBA-911E-50BF7E71C763}">
   <dimension ref="B9:V313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25094,7 +25094,7 @@
         <v>33</v>
       </c>
       <c r="M173">
-        <v>0.24174491286178454</v>
+        <v>0.24174491286178457</v>
       </c>
       <c r="O173" t="s">
         <v>311</v>
@@ -25147,7 +25147,7 @@
         <v>33</v>
       </c>
       <c r="M174">
-        <v>0.24174491286178454</v>
+        <v>0.24174491286178457</v>
       </c>
       <c r="O174" t="s">
         <v>311</v>
@@ -25200,7 +25200,7 @@
         <v>33</v>
       </c>
       <c r="M175">
-        <v>0.24174491286178454</v>
+        <v>0.24174491286178457</v>
       </c>
       <c r="O175" t="s">
         <v>311</v>
@@ -25460,7 +25460,7 @@
         <v>14</v>
       </c>
       <c r="R179" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S179" t="s">
         <v>313</v>
@@ -25522,7 +25522,7 @@
         <v>14</v>
       </c>
       <c r="R180" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S180" t="s">
         <v>313</v>
@@ -25770,7 +25770,7 @@
         <v>14</v>
       </c>
       <c r="R184" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S184" t="s">
         <v>313</v>
@@ -25832,7 +25832,7 @@
         <v>14</v>
       </c>
       <c r="R185" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S185" t="s">
         <v>313</v>
@@ -26824,7 +26824,7 @@
         <v>14</v>
       </c>
       <c r="R201" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S201" t="s">
         <v>313</v>
@@ -26886,7 +26886,7 @@
         <v>14</v>
       </c>
       <c r="R202" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S202" t="s">
         <v>313</v>
@@ -27630,7 +27630,7 @@
         <v>14</v>
       </c>
       <c r="R214" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S214" t="s">
         <v>313</v>
@@ -27692,7 +27692,7 @@
         <v>14</v>
       </c>
       <c r="R215" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S215" t="s">
         <v>313</v>
@@ -27754,7 +27754,7 @@
         <v>14</v>
       </c>
       <c r="R216" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S216" t="s">
         <v>313</v>
@@ -27816,7 +27816,7 @@
         <v>14</v>
       </c>
       <c r="R217" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S217" t="s">
         <v>313</v>
@@ -28436,7 +28436,7 @@
         <v>14</v>
       </c>
       <c r="R227" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S227" t="s">
         <v>313</v>
@@ -28498,7 +28498,7 @@
         <v>14</v>
       </c>
       <c r="R228" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S228" t="s">
         <v>313</v>
@@ -31821,7 +31821,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E1EED8-CA0E-427C-A80D-055AE8015B2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3596EE-53D4-4041-98B5-B64EA804A002}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
+++ b/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E86660C-E27F-4C5D-BBF8-5A48FBDEFA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7374840-9DCF-450E-A606-EC86E285ED90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{45177100-C8EE-494F-9509-F27232C67BAF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{863342C5-67C2-41D5-A7F6-6D9A166241CC}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3028,7 +3028,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0D3EAA-BF38-4F9F-9345-C279A348BCB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A073499-9EC8-4F65-976F-CDE2289FEC89}">
   <dimension ref="B9:V162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12532,7 +12532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{893800B3-8B03-40C2-8796-36AB201097D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BACA8D-0602-4554-B1E1-88764E45DB54}">
   <dimension ref="B9:V57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15457,7 +15457,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{274FF8A8-B03A-4CBA-911E-50BF7E71C763}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DEABFED-273F-4479-BA69-3F3280D59EB7}">
   <dimension ref="B9:V313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25956,7 +25956,7 @@
         <v>14</v>
       </c>
       <c r="R187" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S187" t="s">
         <v>313</v>
@@ -26018,7 +26018,7 @@
         <v>14</v>
       </c>
       <c r="R188" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S188" t="s">
         <v>313</v>
@@ -26824,7 +26824,7 @@
         <v>14</v>
       </c>
       <c r="R201" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S201" t="s">
         <v>313</v>
@@ -26886,7 +26886,7 @@
         <v>14</v>
       </c>
       <c r="R202" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S202" t="s">
         <v>313</v>
@@ -27630,7 +27630,7 @@
         <v>14</v>
       </c>
       <c r="R214" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S214" t="s">
         <v>313</v>
@@ -27692,7 +27692,7 @@
         <v>14</v>
       </c>
       <c r="R215" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S215" t="s">
         <v>313</v>
@@ -27754,7 +27754,7 @@
         <v>14</v>
       </c>
       <c r="R216" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S216" t="s">
         <v>313</v>
@@ -27816,7 +27816,7 @@
         <v>14</v>
       </c>
       <c r="R217" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S217" t="s">
         <v>313</v>
@@ -27878,7 +27878,7 @@
         <v>14</v>
       </c>
       <c r="R218" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S218" t="s">
         <v>313</v>
@@ -27940,7 +27940,7 @@
         <v>14</v>
       </c>
       <c r="R219" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S219" t="s">
         <v>313</v>
@@ -28622,7 +28622,7 @@
         <v>14</v>
       </c>
       <c r="R230" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S230" t="s">
         <v>313</v>
@@ -28684,7 +28684,7 @@
         <v>14</v>
       </c>
       <c r="R231" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S231" t="s">
         <v>313</v>
@@ -31821,7 +31821,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE3596EE-53D4-4041-98B5-B64EA804A002}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D6042E-A4F2-439B-8C9A-C460C60ECA12}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
+++ b/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7374840-9DCF-450E-A606-EC86E285ED90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B7A1933-D7B9-4766-919A-6D5D47053DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{863342C5-67C2-41D5-A7F6-6D9A166241CC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C13D341C-3477-44B8-906B-5487945CA789}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3028,7 +3028,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A073499-9EC8-4F65-976F-CDE2289FEC89}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50A67C23-9478-43FF-B515-F82CEF570BD4}">
   <dimension ref="B9:V162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12532,7 +12532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86BACA8D-0602-4554-B1E1-88764E45DB54}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8BEF250-2925-48A8-B69E-A27B866B96DB}">
   <dimension ref="B9:V57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15457,7 +15457,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DEABFED-273F-4479-BA69-3F3280D59EB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF49C06C-46CE-4851-A44F-485F3D6A87A1}">
   <dimension ref="B9:V313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26824,7 +26824,7 @@
         <v>14</v>
       </c>
       <c r="R201" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S201" t="s">
         <v>313</v>
@@ -26886,7 +26886,7 @@
         <v>14</v>
       </c>
       <c r="R202" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S202" t="s">
         <v>313</v>
@@ -27072,7 +27072,7 @@
         <v>14</v>
       </c>
       <c r="R205" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S205" t="s">
         <v>313</v>
@@ -27134,7 +27134,7 @@
         <v>14</v>
       </c>
       <c r="R206" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S206" t="s">
         <v>313</v>
@@ -27630,7 +27630,7 @@
         <v>14</v>
       </c>
       <c r="R214" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S214" t="s">
         <v>313</v>
@@ -27692,7 +27692,7 @@
         <v>14</v>
       </c>
       <c r="R215" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S215" t="s">
         <v>313</v>
@@ -28436,7 +28436,7 @@
         <v>14</v>
       </c>
       <c r="R227" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S227" t="s">
         <v>313</v>
@@ -28498,7 +28498,7 @@
         <v>14</v>
       </c>
       <c r="R228" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S228" t="s">
         <v>313</v>
@@ -31821,7 +31821,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D6042E-A4F2-439B-8C9A-C460C60ECA12}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83297BBE-35DB-4BF3-9640-CC3F982C17D9}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
+++ b/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B7A1933-D7B9-4766-919A-6D5D47053DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D993C5A-712A-4B46-A8EA-02D4167B01E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C13D341C-3477-44B8-906B-5487945CA789}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{97EC63FF-E812-4843-AC67-4E518B47EA04}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3028,7 +3028,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50A67C23-9478-43FF-B515-F82CEF570BD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061E4B61-80BF-499D-A3E5-4277E673D49B}">
   <dimension ref="B9:V162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12532,7 +12532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8BEF250-2925-48A8-B69E-A27B866B96DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6FC201C-518B-48D2-B637-5CAFA529AE90}">
   <dimension ref="B9:V57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15457,7 +15457,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF49C06C-46CE-4851-A44F-485F3D6A87A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA46055C-23E3-4EEE-AA71-D4B7A40F0765}">
   <dimension ref="B9:V313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25460,7 +25460,7 @@
         <v>14</v>
       </c>
       <c r="R179" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S179" t="s">
         <v>313</v>
@@ -25522,7 +25522,7 @@
         <v>14</v>
       </c>
       <c r="R180" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S180" t="s">
         <v>313</v>
@@ -27072,7 +27072,7 @@
         <v>14</v>
       </c>
       <c r="R205" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S205" t="s">
         <v>313</v>
@@ -27134,7 +27134,7 @@
         <v>14</v>
       </c>
       <c r="R206" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S206" t="s">
         <v>313</v>
@@ -28622,7 +28622,7 @@
         <v>14</v>
       </c>
       <c r="R230" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S230" t="s">
         <v>313</v>
@@ -28684,7 +28684,7 @@
         <v>14</v>
       </c>
       <c r="R231" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S231" t="s">
         <v>313</v>
@@ -31821,7 +31821,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83297BBE-35DB-4BF3-9640-CC3F982C17D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD5788BF-EB59-4E89-8706-5634DAA3D016}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
+++ b/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D993C5A-712A-4B46-A8EA-02D4167B01E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{600A4350-A010-47BF-BB6F-3F1559F30B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{97EC63FF-E812-4843-AC67-4E518B47EA04}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EB6DADE7-E4DC-4A68-806F-8D5718A641B8}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3028,7 +3028,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061E4B61-80BF-499D-A3E5-4277E673D49B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7C1F8-FA01-4D3F-892A-063C0499B890}">
   <dimension ref="B9:V162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12532,7 +12532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6FC201C-518B-48D2-B637-5CAFA529AE90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCBB163E-BA42-441D-A2FC-1B9370A2CB55}">
   <dimension ref="B9:V57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15457,7 +15457,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA46055C-23E3-4EEE-AA71-D4B7A40F0765}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2B03AF0-B027-4FD9-A515-A773264BDF84}">
   <dimension ref="B9:V313"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25770,7 +25770,7 @@
         <v>14</v>
       </c>
       <c r="R184" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S184" t="s">
         <v>313</v>
@@ -25832,7 +25832,7 @@
         <v>14</v>
       </c>
       <c r="R185" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S185" t="s">
         <v>313</v>
@@ -27072,7 +27072,7 @@
         <v>14</v>
       </c>
       <c r="R205" t="s">
-        <v>484</v>
+        <v>424</v>
       </c>
       <c r="S205" t="s">
         <v>313</v>
@@ -27134,7 +27134,7 @@
         <v>14</v>
       </c>
       <c r="R206" t="s">
-        <v>424</v>
+        <v>484</v>
       </c>
       <c r="S206" t="s">
         <v>313</v>
@@ -31821,7 +31821,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD5788BF-EB59-4E89-8706-5634DAA3D016}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8B4ED9B-5D32-457D-9D52-BCC892555751}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
+++ b/VerveStacks_ZAF_grids_kan/vt_vervestacks_ZAF_v1.xlsx
@@ -5,18 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{600A4350-A010-47BF-BB6F-3F1559F30B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7BE0C2-7996-4058-B98F-C0ABF2C57A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EB6DADE7-E4DC-4A68-806F-8D5718A641B8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{EB6DADE7-E4DC-4A68-806F-8D5718A641B8}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
     <sheet name="new_options" sheetId="3" r:id="rId2"/>
     <sheet name="existing_stock" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5573" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5573" uniqueCount="874">
   <si>
     <t>~fi_t</t>
   </si>
@@ -2658,6 +2657,12 @@
   </si>
   <si>
     <t>ccs retrofit of -- Ankerlig power station_1-2 -- operating</t>
+  </si>
+  <si>
+    <t>DeACTfi_t</t>
+  </si>
+  <si>
+    <t>DeACTfi_process</t>
   </si>
 </sst>
 </file>
@@ -3034,10 +3039,10 @@
   <sheetData>
     <row r="9" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>0</v>
+        <v>872</v>
       </c>
       <c r="O9" t="s">
-        <v>304</v>
+        <v>873</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.45">
@@ -12535,6 +12540,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCBB163E-BA42-441D-A2FC-1B9370A2CB55}">
   <dimension ref="B9:V57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="39.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="9" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
@@ -31818,13 +31829,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8B4ED9B-5D32-457D-9D52-BCC892555751}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>